--- a/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/LTC6102_Param.xlsx
+++ b/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/LTC6102_Param.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD12_JIG\XD12_PWM\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_PWM_Rev_0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F91F00E-F2DA-4814-93E3-80CBAB7A996F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A53281A-DA6B-456E-A8D3-5775D49E7CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{11FFDA7F-9C68-49B0-9D76-D5DA7C94FBB9}"/>
+    <workbookView xWindow="4620" yWindow="293" windowWidth="16050" windowHeight="12764" activeTab="1" xr2:uid="{11FFDA7F-9C68-49B0-9D76-D5DA7C94FBB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Org" sheetId="1" r:id="rId1"/>
@@ -3399,11 +3399,11 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" si="0"/>
-        <v>3.4180209048599985E-3</v>
+        <v>1.5869382772564279E-3</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="1"/>
-        <v>5.1270313572899977E-3</v>
+        <v>2.380407415884642E-3</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" ref="O5:O27" si="7">ROUND((N5/1000)/$E$3*$D$3, 0)</f>
@@ -3456,7 +3456,7 @@
         <v>200</v>
       </c>
       <c r="D6" s="12">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E6" s="24">
         <v>2200</v>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" si="0"/>
-        <v>6.8360418097199969E-3</v>
+        <v>3.1738765545128557E-3</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="1"/>
-        <v>1.0254062714579995E-2</v>
+        <v>4.760814831769284E-3</v>
       </c>
       <c r="O6" s="1">
         <f t="shared" si="7"/>
@@ -3532,11 +3532,11 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>1.0254062714579994E-2</v>
+        <v>4.7608148317692832E-3</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="1"/>
-        <v>1.5381094071869989E-2</v>
+        <v>7.1412222476539243E-3</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" si="7"/>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>1.3672083619439994E-2</v>
+        <v>6.3477531090257115E-3</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="1"/>
-        <v>2.0508125429159991E-2</v>
+        <v>9.521629663538568E-3</v>
       </c>
       <c r="O8" s="1">
         <f t="shared" si="7"/>
@@ -3669,31 +3669,31 @@
         <v>23</v>
       </c>
       <c r="C9" s="4">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="D9" s="11">
         <f>C9*$D$6/1000</f>
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="E9" s="5">
         <f>C9*D6/$E$6</f>
-        <v>0.89090909090909087</v>
+        <v>0.82727272727272727</v>
       </c>
       <c r="F9" s="2">
         <f>D9/$E$6*$F$6</f>
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="G9" s="1">
         <f>$D9*$D9/D6</f>
-        <v>0.13719999999999999</v>
+        <v>0.25480000000000003</v>
       </c>
       <c r="H9" s="8">
         <f>C9/(F9/$E$3*$D$3)*1000</f>
-        <v>3.6331558899996659</v>
+        <v>7.825258839999278</v>
       </c>
       <c r="I9" s="20">
         <f>F9/$E$3*$D$3</f>
-        <v>19266.995999999999</v>
+        <v>17890.782000000003</v>
       </c>
       <c r="K9" s="7">
         <v>5</v>
@@ -3704,11 +3704,11 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>1.7090104524299994E-2</v>
+        <v>7.9346913862821389E-3</v>
       </c>
       <c r="N9" s="14">
         <f t="shared" si="1"/>
-        <v>2.5635156786449991E-2</v>
+        <v>1.1902037079423208E-2</v>
       </c>
       <c r="O9" s="1">
         <f t="shared" si="7"/>
@@ -3793,11 +3793,11 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>2.0508125429159987E-2</v>
+        <v>9.5216296635385663E-3</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="1"/>
-        <v>3.0762188143739978E-2</v>
+        <v>1.4282444495307849E-2</v>
       </c>
       <c r="O10" s="1">
         <f t="shared" si="7"/>
@@ -3882,11 +3882,11 @@
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
-        <v>2.3926146334019991E-2</v>
+        <v>1.1108567940794995E-2</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="1"/>
-        <v>3.5889219501029988E-2</v>
+        <v>1.6662851911192492E-2</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" si="7"/>
@@ -3941,11 +3941,11 @@
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>2.7344167238879988E-2</v>
+        <v>1.2695506218051423E-2</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="1"/>
-        <v>4.1016250858319982E-2</v>
+        <v>1.9043259327077136E-2</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="7"/>
@@ -4015,11 +4015,11 @@
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>3.0762188143739991E-2</v>
+        <v>1.4282444495307852E-2</v>
       </c>
       <c r="N13" s="14">
         <f t="shared" si="1"/>
-        <v>4.6143282215609989E-2</v>
+        <v>2.142366674296178E-2</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="7"/>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="E14" s="9">
         <f>C14/$D$6</f>
-        <v>0.42857142857142855</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="F14" s="1">
         <f>ROUND(E14/$H$9, 0)</f>
@@ -4093,11 +4093,11 @@
       </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>3.4180209048599988E-2</v>
+        <v>1.5869382772564278E-2</v>
       </c>
       <c r="N14" s="14">
         <f t="shared" si="1"/>
-        <v>5.1270313572899982E-2</v>
+        <v>2.3804074158846417E-2</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" si="7"/>
@@ -4171,15 +4171,15 @@
       </c>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>6.8360418097199976E-2</v>
+        <v>3.1738765545128556E-2</v>
       </c>
       <c r="N15" s="14">
         <f t="shared" si="1"/>
-        <v>0.10254062714579996</v>
+        <v>4.7608148317692833E-2</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="7">
@@ -4249,15 +4249,15 @@
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>0.10254062714579995</v>
+        <v>4.760814831769284E-2</v>
       </c>
       <c r="N16" s="14">
         <f t="shared" si="1"/>
-        <v>0.15381094071869994</v>
+        <v>7.1412222476539264E-2</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="7">
@@ -4309,15 +4309,15 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>0.17090104524299993</v>
+        <v>7.9346913862821389E-2</v>
       </c>
       <c r="N17" s="14">
         <f t="shared" si="1"/>
-        <v>0.25635156786449986</v>
+        <v>0.11902037079423208</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="7">
         <v>100</v>
@@ -4368,15 +4368,15 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>0.34180209048599985</v>
+        <v>0.15869382772564278</v>
       </c>
       <c r="N18" s="14">
         <f t="shared" si="1"/>
-        <v>0.51270313572899973</v>
+        <v>0.23804074158846417</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="7">
         <v>150</v>
@@ -4443,15 +4443,15 @@
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>0.68360418097199971</v>
+        <v>0.31738765545128556</v>
       </c>
       <c r="N19" s="14">
         <f t="shared" si="1"/>
-        <v>1.0254062714579995</v>
+        <v>0.47608148317692833</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="7">
         <v>200</v>
@@ -4520,15 +4520,15 @@
       </c>
       <c r="M20" s="18">
         <f t="shared" si="0"/>
-        <v>1.0254062714579995</v>
+        <v>0.47608148317692833</v>
       </c>
       <c r="N20" s="14">
         <f t="shared" si="1"/>
-        <v>1.5381094071869992</v>
+        <v>0.71412222476539255</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="7">
         <v>300</v>
@@ -4601,15 +4601,15 @@
       </c>
       <c r="M21" s="18">
         <f t="shared" si="0"/>
-        <v>1.7090104524299994</v>
+        <v>0.793469138628214</v>
       </c>
       <c r="N21" s="14">
         <f t="shared" si="1"/>
-        <v>2.5635156786449991</v>
+        <v>1.1902037079423209</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q21" s="7">
         <v>500</v>
@@ -4682,15 +4682,15 @@
       </c>
       <c r="M22" s="18">
         <f t="shared" si="0"/>
-        <v>3.4180209048599988</v>
+        <v>1.586938277256428</v>
       </c>
       <c r="N22" s="14">
         <f t="shared" si="1"/>
-        <v>5.1270313572899981</v>
+        <v>2.3804074158846418</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="7">
         <v>1000</v>
@@ -4764,15 +4764,15 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>6.8360418097199975</v>
+        <v>3.173876554512856</v>
       </c>
       <c r="N23" s="14">
         <f t="shared" si="1"/>
-        <v>10.254062714579996</v>
+        <v>4.7608148317692836</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" si="7"/>
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="Q23" s="7">
         <v>2000</v>
@@ -4845,15 +4845,15 @@
       </c>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>17.090104524299992</v>
+        <v>7.9346913862821395</v>
       </c>
       <c r="N24" s="14">
         <f t="shared" si="1"/>
-        <v>25.63515678644999</v>
+        <v>11.902037079423209</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="7"/>
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="P24" s="17"/>
       <c r="Q24" s="7">
@@ -4906,15 +4906,15 @@
       </c>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>34.180209048599984</v>
+        <v>15.869382772564279</v>
       </c>
       <c r="N25" s="14">
         <f t="shared" si="1"/>
-        <v>51.27031357289998</v>
+        <v>23.804074158846419</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" si="7"/>
-        <v>336</v>
+        <v>156</v>
       </c>
       <c r="P25" s="17"/>
       <c r="Q25" s="7">
@@ -4966,15 +4966,15 @@
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>102.54062714579996</v>
+        <v>47.608148317692837</v>
       </c>
       <c r="N26" s="14">
         <f t="shared" si="1"/>
-        <v>153.81094071869992</v>
+        <v>71.412222476539256</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="7"/>
-        <v>1008</v>
+        <v>468</v>
       </c>
       <c r="Q26" s="7">
         <v>30000</v>
@@ -5025,15 +5025,15 @@
       </c>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>224</v>
+        <v>104</v>
       </c>
       <c r="N27" s="14">
         <f t="shared" si="1"/>
-        <v>336</v>
+        <v>156</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="7"/>
-        <v>2202</v>
+        <v>1022</v>
       </c>
       <c r="Q27" s="7">
         <v>65535</v>

--- a/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/LTC6102_Param.xlsx
+++ b/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/LTC6102_Param.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_PWM_Rev_0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A53281A-DA6B-456E-A8D3-5775D49E7CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785817AA-981A-4C2E-A1CC-0DA5CFBAF76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="293" windowWidth="16050" windowHeight="12764" activeTab="1" xr2:uid="{11FFDA7F-9C68-49B0-9D76-D5DA7C94FBB9}"/>
+    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{11FFDA7F-9C68-49B0-9D76-D5DA7C94FBB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Org" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="176" formatCode="0&quot;mA&quot;"/>
     <numFmt numFmtId="177" formatCode="0.000&quot;V&quot;"/>
     <numFmt numFmtId="178" formatCode="0.0&quot;mA&quot;"/>
@@ -360,6 +360,7 @@
     <numFmt numFmtId="191" formatCode="0.00000&quot;V&quot;"/>
     <numFmt numFmtId="192" formatCode="0.0000000&quot;V&quot;"/>
     <numFmt numFmtId="193" formatCode="0.0&quot;Ω&quot;"/>
+    <numFmt numFmtId="209" formatCode="0.000000000_);[Red]\(0.000000000\)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -417,7 +418,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -500,6 +501,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="209" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3171,7 +3175,7 @@
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="1" bestFit="1" customWidth="1"/>
@@ -5075,6 +5079,10 @@
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.6">
+      <c r="C28" s="28">
+        <f>E9/D3</f>
+        <v>2.5247130566506768E-5</v>
+      </c>
       <c r="P28" s="17"/>
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
